--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_16/design_variables_statistics.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_16/design_variables_statistics.xlsx
@@ -495,31 +495,31 @@
         <v>50</v>
       </c>
       <c r="C2" t="n">
-        <v>79.39</v>
+        <v>81.41</v>
       </c>
       <c r="D2" t="n">
-        <v>11.58</v>
+        <v>10.82</v>
       </c>
       <c r="E2" t="n">
-        <v>14.58</v>
+        <v>13.29</v>
       </c>
       <c r="F2" t="n">
-        <v>63.44</v>
+        <v>66.72</v>
       </c>
       <c r="G2" t="n">
-        <v>68.37</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>78.31</v>
+        <v>82.31</v>
       </c>
       <c r="I2" t="n">
-        <v>88.73999999999999</v>
+        <v>90.64</v>
       </c>
       <c r="J2" t="n">
         <v>100</v>
       </c>
       <c r="K2" t="n">
-        <v>36.56</v>
+        <v>33.28</v>
       </c>
     </row>
     <row r="3">
@@ -532,31 +532,31 @@
         <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>48.62</v>
+        <v>45.59</v>
       </c>
       <c r="D3" t="n">
-        <v>0.64</v>
+        <v>0.39</v>
       </c>
       <c r="E3" t="n">
-        <v>1.31</v>
+        <v>0.85</v>
       </c>
       <c r="F3" t="n">
-        <v>47.2</v>
+        <v>45.42</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6</v>
+        <v>45.42</v>
       </c>
       <c r="H3" t="n">
-        <v>48.78</v>
+        <v>45.43</v>
       </c>
       <c r="I3" t="n">
-        <v>48.84</v>
+        <v>45.54</v>
       </c>
       <c r="J3" t="n">
-        <v>49.54</v>
+        <v>47.03</v>
       </c>
       <c r="K3" t="n">
-        <v>2.35</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="4">
@@ -569,31 +569,31 @@
         <v>50</v>
       </c>
       <c r="C4" t="n">
-        <v>9.51</v>
+        <v>8.66</v>
       </c>
       <c r="D4" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="E4" t="n">
-        <v>27.93</v>
+        <v>30.43</v>
       </c>
       <c r="F4" t="n">
-        <v>5.01</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>7.08</v>
+        <v>6.36</v>
       </c>
       <c r="H4" t="n">
-        <v>10.1</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>11.83</v>
+        <v>11.04</v>
       </c>
       <c r="J4" t="n">
-        <v>13.48</v>
+        <v>12.09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.470000000000001</v>
+        <v>7.09</v>
       </c>
     </row>
     <row r="5">
@@ -606,31 +606,31 @@
         <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>97.19</v>
+        <v>55.3</v>
       </c>
       <c r="D5" t="n">
-        <v>42.48</v>
+        <v>12.75</v>
       </c>
       <c r="E5" t="n">
-        <v>43.71</v>
+        <v>23.07</v>
       </c>
       <c r="F5" t="n">
-        <v>36.88</v>
+        <v>36.27</v>
       </c>
       <c r="G5" t="n">
-        <v>75.09999999999999</v>
+        <v>43.44</v>
       </c>
       <c r="H5" t="n">
-        <v>83.05</v>
+        <v>56.39</v>
       </c>
       <c r="I5" t="n">
-        <v>118.17</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>199.95</v>
+        <v>74.14</v>
       </c>
       <c r="K5" t="n">
-        <v>163.07</v>
+        <v>37.87</v>
       </c>
     </row>
     <row r="6">
@@ -643,31 +643,31 @@
         <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>3.67</v>
+        <v>3.95</v>
       </c>
       <c r="D6" t="n">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="E6" t="n">
-        <v>25.06</v>
+        <v>24.13</v>
       </c>
       <c r="F6" t="n">
-        <v>2.19</v>
+        <v>2.11</v>
       </c>
       <c r="G6" t="n">
-        <v>2.68</v>
+        <v>3.82</v>
       </c>
       <c r="H6" t="n">
-        <v>3.81</v>
+        <v>4.29</v>
       </c>
       <c r="I6" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="J6" t="n">
-        <v>4.96</v>
+        <v>4.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
